--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532112.2107016216</v>
+        <v>532112</v>
       </c>
       <c r="R2" t="n">
-        <v>6356431.394257378</v>
+        <v>6356431</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105670</v>
+        <v>105675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105675</v>
+        <v>105683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51587-2024 artfynd.xlsx
+++ b/artfynd/A 51587-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74120280</v>
       </c>
       <c r="B2" t="n">
-        <v>105683</v>
+        <v>105693</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
